--- a/JAMS/Results Analysis/market_potential.xlsx
+++ b/JAMS/Results Analysis/market_potential.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DESKTOP\Desktop\Github\Raster_PV_Poten\JAMS\Results Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sidus\Desktop\GRI Github\Raster_PV_Poten\JAMS\Results Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD4C2F7-2E8B-4AC8-8FA5-5E90F4F3F3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F015277-9C71-4F8D-BED7-9CD9E6562C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" activeTab="1" xr2:uid="{BA61C4E7-4205-4781-84E1-4182DA752654}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BA61C4E7-4205-4781-84E1-4182DA752654}"/>
   </bookViews>
   <sheets>
     <sheet name="데이터" sheetId="1" r:id="rId1"/>
@@ -136,50 +136,50 @@
   </si>
   <si>
     <t>rooftop_PV</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>grmt_PV</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>units</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>type</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SGG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>휘문박사님이 준 raster파일에서 zonal statistics로 분류</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>class</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>market</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>MWh</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -187,11 +187,6 @@
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -232,8 +227,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -569,13 +564,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80D418E4-1BE8-4BD4-865F-2F9162264E61}">
   <dimension ref="A1:E63"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -592,1062 +587,1062 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="1">
-        <v>242764.38033103835</v>
+      <c r="D2" s="2">
+        <v>242698.66718816801</v>
       </c>
       <c r="E2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="1">
-        <v>187992.58489227219</v>
+      <c r="D3" s="2">
+        <v>187979.14951849019</v>
       </c>
       <c r="E3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1">
-        <v>1161502.9351901927</v>
+      <c r="D4" s="2">
+        <v>1146641.571169846</v>
       </c>
       <c r="E4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1">
-        <v>18552.020915985137</v>
+      <c r="D5" s="2">
+        <v>18349.348114967361</v>
       </c>
       <c r="E5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="1">
-        <v>83773.141311645217</v>
+      <c r="D6" s="2">
+        <v>83766.438655853344</v>
       </c>
       <c r="E6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="1">
-        <v>140494.18543291112</v>
+      <c r="D7" s="2">
+        <v>140421.40761709161</v>
       </c>
       <c r="E7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1">
-        <v>631968.47363710555</v>
+      <c r="D8" s="2">
+        <v>631420.42559528118</v>
       </c>
       <c r="E8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="1">
-        <v>219512.9670000078</v>
+      <c r="D9" s="2">
+        <v>219506.34396219251</v>
       </c>
       <c r="E9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="1">
-        <v>718972.37467050506</v>
+      <c r="D10" s="2">
+        <v>718811.32597923477</v>
       </c>
       <c r="E10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="1">
-        <v>181248.27327871291</v>
+      <c r="D11" s="2">
+        <v>181234.95801496459</v>
       </c>
       <c r="E11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="1">
-        <v>127273.02316379544</v>
+      <c r="D12" s="2">
+        <v>127159.67867040601</v>
       </c>
       <c r="E12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="1">
-        <v>298166.58718490589</v>
+      <c r="D13" s="2">
+        <v>298100.4602308278</v>
       </c>
       <c r="E13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="1">
-        <v>1097752.4861326173</v>
+      <c r="D14" s="2">
+        <v>1095758.856987956</v>
       </c>
       <c r="E14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="1">
-        <v>134224.79177570343</v>
+      <c r="D15" s="2">
+        <v>134159.12447786369</v>
       </c>
       <c r="E15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="1">
-        <v>703300.31254863192</v>
+      <c r="D16" s="2">
+        <v>685654.75813340896</v>
       </c>
       <c r="E16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="1">
-        <v>927117.88536071696</v>
+      <c r="D17" s="2">
+        <v>925986.99779129121</v>
       </c>
       <c r="E17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="1">
-        <v>1908651.0390367475</v>
+      <c r="D18" s="2">
+        <v>1899948.6858606201</v>
       </c>
       <c r="E18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="1">
-        <v>14008.984489917751</v>
+      <c r="D19" s="2">
+        <v>13989.242919445051</v>
       </c>
       <c r="E19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="1">
-        <v>326405.52080821886</v>
+      <c r="D20" s="2">
+        <v>326064.50272226171</v>
       </c>
       <c r="E20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C21" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="1">
-        <v>251140.48545265244</v>
+      <c r="D21" s="2">
+        <v>248919.92376423001</v>
       </c>
       <c r="E21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="1">
-        <v>272118.25614500028</v>
+      <c r="D22" s="2">
+        <v>272026.44053888333</v>
       </c>
       <c r="E22" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="1">
-        <v>203041.55695915158</v>
+      <c r="D23" s="2">
+        <v>202194.66302490159</v>
       </c>
       <c r="E23" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="1">
-        <v>173639.59098577563</v>
+      <c r="D24" s="2">
+        <v>173303.9138140686</v>
       </c>
       <c r="E24" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="1">
-        <v>147465.55329275114</v>
+      <c r="D25" s="2">
+        <v>147280.94407653809</v>
       </c>
       <c r="E25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="1">
-        <v>826816.42190599267</v>
+      <c r="D26" s="2">
+        <v>826730.29815530579</v>
       </c>
       <c r="E26" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="1">
-        <v>555025.75723075564</v>
+      <c r="D27" s="2">
+        <v>553474.349813462</v>
       </c>
       <c r="E27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="1">
-        <v>323996.74038076319</v>
+      <c r="D28" s="2">
+        <v>323876.91416025098</v>
       </c>
       <c r="E28" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="2">
         <v>531581.19717407273</v>
       </c>
       <c r="E29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="1">
-        <v>854884.27754258853</v>
+      <c r="D30" s="2">
+        <v>854836.3707966794</v>
       </c>
       <c r="E30" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="1">
-        <v>971640.94120216044</v>
+      <c r="D31" s="2">
+        <v>970511.26822234422</v>
       </c>
       <c r="E31" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="1">
-        <v>803968.0160455677</v>
+      <c r="D32" s="2">
+        <v>802598.09709978173</v>
       </c>
       <c r="E32" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C33" t="s">
         <v>32</v>
       </c>
       <c r="D33" s="2">
-        <v>192684.01480007276</v>
+        <v>187152.1542587282</v>
       </c>
       <c r="E33" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C34" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>25524.919095039408</v>
+        <v>25365.508142471299</v>
       </c>
       <c r="E34" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C35" t="s">
         <v>32</v>
       </c>
       <c r="D35" s="2">
-        <v>739349.27753257821</v>
+        <v>491551.59650230478</v>
       </c>
       <c r="E35" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C36" t="s">
         <v>32</v>
       </c>
       <c r="D36" s="2">
-        <v>285665.73859501013</v>
+        <v>267305.37611961481</v>
       </c>
       <c r="E36" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C37" t="s">
         <v>32</v>
       </c>
       <c r="D37" s="2">
-        <v>37601.958534240788</v>
+        <v>37486.985255241423</v>
       </c>
       <c r="E37" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C38" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="2">
-        <v>41634.856530189514</v>
+        <v>39620.472106933652</v>
       </c>
       <c r="E38" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C39" t="s">
         <v>32</v>
       </c>
       <c r="D39" s="2">
-        <v>818459.87703228393</v>
+        <v>796583.71603583673</v>
       </c>
       <c r="E39" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C40" t="s">
         <v>32</v>
       </c>
       <c r="D40" s="2">
-        <v>44548.823874473732</v>
+        <v>43385.35837841023</v>
       </c>
       <c r="E40" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
       </c>
       <c r="D41" s="2">
-        <v>527020.25867080153</v>
+        <v>522639.13496875449</v>
       </c>
       <c r="E41" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
       </c>
       <c r="D42" s="2">
-        <v>81961.191822052147</v>
+        <v>81563.406555175476</v>
       </c>
       <c r="E42" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
       </c>
       <c r="D43" s="2">
-        <v>148315.38442897826</v>
+        <v>147359.78625583631</v>
       </c>
       <c r="E43" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
       </c>
       <c r="D44" s="2">
-        <v>170015.09819793599</v>
+        <v>168887.5701389309</v>
       </c>
       <c r="E44" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
       </c>
       <c r="D45" s="2">
-        <v>4663873.2124128686</v>
+        <v>3643818.454106329</v>
       </c>
       <c r="E45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
       </c>
       <c r="D46" s="2">
-        <v>1873291.9460811412</v>
+        <v>1754327.0347328449</v>
       </c>
       <c r="E46" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
       </c>
       <c r="D47" s="2">
-        <v>4048221.0930548254</v>
+        <v>3804218.1815368379</v>
       </c>
       <c r="E47" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
       </c>
       <c r="D48" s="2">
-        <v>476998.03759002587</v>
+        <v>427404.5115747446</v>
       </c>
       <c r="E48" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
       </c>
       <c r="D49" s="2">
-        <v>2425637.5416193218</v>
+        <v>2338998.7937993868</v>
       </c>
       <c r="E49" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
       </c>
       <c r="D50" s="2">
-        <v>25553.154950141859</v>
+        <v>22852.316383361878</v>
       </c>
       <c r="E50" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C51" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="2">
-        <v>934352.69893073896</v>
+        <v>880578.07169818459</v>
       </c>
       <c r="E51" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C52" t="s">
         <v>32</v>
       </c>
       <c r="D52" s="2">
-        <v>4433508.8843049621</v>
+        <v>3816489.273055112</v>
       </c>
       <c r="E52" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
       </c>
       <c r="D53" s="2">
-        <v>2627040.6952800364</v>
+        <v>2414826.5945053352</v>
       </c>
       <c r="E53" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C54" t="s">
         <v>32</v>
       </c>
       <c r="D54" s="2">
-        <v>7496621.0559034245</v>
+        <v>6686299.9649914755</v>
       </c>
       <c r="E54" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
       </c>
       <c r="D55" s="2">
-        <v>1989123.0413494378</v>
+        <v>1848580.175203328</v>
       </c>
       <c r="E55" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
       </c>
       <c r="D56" s="2">
-        <v>2275826.7404480088</v>
+        <v>2087870.4199953601</v>
       </c>
       <c r="E56" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
       </c>
       <c r="D57" s="2">
-        <v>51236.372063636823</v>
+        <v>51210.05498123174</v>
       </c>
       <c r="E57" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
       </c>
       <c r="D58" s="2">
-        <v>212405.49813461225</v>
+        <v>188894.04282951311</v>
       </c>
       <c r="E58" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
       </c>
       <c r="D59" s="2">
-        <v>59434.143446922215</v>
+        <v>57360.85405540494</v>
       </c>
       <c r="E59" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
       </c>
       <c r="D60" s="2">
-        <v>15312.267420768738</v>
+        <v>15312.26742076874</v>
       </c>
       <c r="E60" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="2">
-        <v>599324.19746017421</v>
+        <v>591124.10235404852</v>
       </c>
       <c r="E61" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
       </c>
       <c r="D62" s="2">
-        <v>217800.90323639015</v>
+        <v>211484.13841056879</v>
       </c>
       <c r="E62" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
       </c>
       <c r="D63" s="2">
-        <v>1002122.9595413235</v>
+        <v>978704.90029812569</v>
       </c>
       <c r="E63" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1655,15 +1650,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{128B25D7-1C95-4EFA-B975-B6C1544FB31D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>